--- a/template/agg.xlsx
+++ b/template/agg.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\Research\Automate\quantum_spherical_fuzzy_tool\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80B7B785-AF5C-4B4E-83B5-F0FF49F73F2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4A02E3D-F0E4-437A-B64B-197D959AD2E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="4">
   <si>
     <t>(0,4ej2p0,4; 0,31623ej2p0,25; 0,86023ej2p0,35)</t>
   </si>
@@ -354,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
@@ -377,6 +377,66 @@
         <v>3</v>
       </c>
     </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
